--- a/rules/CORE-000540/negative/02/data/unit-test-coreid-CG0333-negative 2.xlsx
+++ b/rules/CORE-000540/negative/02/data/unit-test-coreid-CG0333-negative 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000540\negative\02\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6472C65-4DED-48C3-8AEC-3F5B6865A56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9CAA2BE-9924-4BBC-BBB5-7911BB94D7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32025" yWindow="3960" windowWidth="21600" windowHeight="8295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="82">
   <si>
     <t>Product</t>
   </si>
@@ -265,6 +265,12 @@
   </si>
   <si>
     <t>FACM</t>
+  </si>
+  <si>
+    <t>$list_dataset_names</t>
+  </si>
+  <si>
+    <t>fa, facm, fa1</t>
   </si>
 </sst>
 </file>
@@ -744,7 +750,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -785,6 +791,26 @@
       </c>
       <c r="F2" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
